--- a/artfynd/A 54887-2023 artfynd.xlsx
+++ b/artfynd/A 54887-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54887-2023 artfynd.xlsx
+++ b/artfynd/A 54887-2023 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90839572</v>
+        <v>90839549</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sikåskälen-Anders-Anderssonbodarna_S, Jmt</t>
+          <t>SIkåskälen-Anders_Anderssonbodarna_S, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>504091.1453230695</v>
+        <v>503860</v>
       </c>
       <c r="R2" t="n">
-        <v>7055062.215638468</v>
+        <v>7055118</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,26 +743,11 @@
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Vid dike/uträtad bäck</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -776,6 +756,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Möjlig kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Granhögstubbe</t>
+        </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -804,16 +794,11 @@
         <v>90839477</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -841,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>503860.8984595275</v>
+        <v>503861</v>
       </c>
       <c r="R3" t="n">
-        <v>7055089.053261657</v>
+        <v>7055089</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +859,9 @@
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-08-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,15 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90839579</v>
+        <v>90839469</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -943,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>219880</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504155.0237287753</v>
+        <v>503919</v>
       </c>
       <c r="R4" t="n">
-        <v>7054907.985090428</v>
+        <v>7054776</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1000,19 +970,9 @@
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-08-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,50 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90839549</v>
+        <v>90839577</v>
       </c>
       <c r="B5" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>219880</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>SIkåskälen-Anders_Anderssonbodarna_S, Jmt</t>
+          <t>Sikåskälen-Anders-Anderssonbodarna_S, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503859.9726959361</v>
+        <v>504155</v>
       </c>
       <c r="R5" t="n">
-        <v>7055117.957061402</v>
+        <v>7054908</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1121,21 +1076,11 @@
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1144,16 +1089,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Möjlig kalkbarrskog</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Granhögstubbe</t>
-        </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -1179,15 +1114,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>90839469</v>
+        <v>90921852</v>
       </c>
       <c r="B6" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,17 +1145,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sikåskälen-Anders-Anderssonbodarna_S, Jmt</t>
+          <t>SIkåskälen-Anders_Anderssonbodarna_S, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503919.1724021534</v>
+        <v>503981</v>
       </c>
       <c r="R6" t="n">
-        <v>7054776.045324611</v>
+        <v>7054777</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1252,21 +1182,11 @@
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1275,6 +1195,11 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Örtrikt stråk</t>
+        </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -1300,15 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>90839531</v>
+        <v>90839572</v>
       </c>
       <c r="B7" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,21 +1236,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1340,10 +1260,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>503929.9159521454</v>
+        <v>504091</v>
       </c>
       <c r="R7" t="n">
-        <v>7054731.139866617</v>
+        <v>7055062</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1373,19 +1293,14 @@
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Vid dike/uträtad bäck</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,15 +1336,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>90839577</v>
+        <v>90839579</v>
       </c>
       <c r="B8" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1437,21 +1347,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1461,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>504155.0237287753</v>
+        <v>504155</v>
       </c>
       <c r="R8" t="n">
-        <v>7054907.985090428</v>
+        <v>7054908</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,19 +1404,9 @@
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-08-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1542,15 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>90921852</v>
+        <v>90921853</v>
       </c>
       <c r="B9" t="n">
-        <v>96660</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,21 +1453,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219880</v>
+        <v>222498</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1582,10 +1477,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>503981.0718819745</v>
+        <v>503981</v>
       </c>
       <c r="R9" t="n">
-        <v>7054777.011919214</v>
+        <v>7054777</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1615,19 +1510,9 @@
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2019-08-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1668,15 +1553,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>90921853</v>
+        <v>90839531</v>
       </c>
       <c r="B10" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1684,37 +1564,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>SIkåskälen-Anders_Anderssonbodarna_S, Jmt</t>
+          <t>Sikåskälen-Anders-Anderssonbodarna_S, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>503981.0718819745</v>
+        <v>503930</v>
       </c>
       <c r="R10" t="n">
-        <v>7054777.011919214</v>
+        <v>7054731</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1741,21 +1621,11 @@
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2019-08-21</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1764,11 +1634,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Örtrikt stråk</t>
-        </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>

--- a/artfynd/A 54887-2023 artfynd.xlsx
+++ b/artfynd/A 54887-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839549</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -899,6 +909,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839469</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1111,6 +1131,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839577</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1222,6 +1247,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921852</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1333,6 +1363,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839572</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1439,6 +1474,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839579</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1550,6 +1590,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90921853</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1656,8 +1701,24 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90839531</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>